--- a/ConfigWorkspace/Data/weapon.xlsx
+++ b/ConfigWorkspace/Data/weapon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB662F78-AFD4-4601-B64D-1399E7461216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC66D3F-B149-4329-8C47-7CEE9C6E1399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>普通</t>
   </si>
   <si>
-    <t>Settings/Renderer2D.asset</t>
-  </si>
-  <si>
     <t>铁剑</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>攻速（0.1~5，必填）</t>
+  </si>
+  <si>
+    <t>Resources\Icons\sardline.png</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -525,10 +525,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
@@ -540,7 +540,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -589,22 +589,22 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -630,7 +630,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J5" s="1">
         <v>0.8</v>
@@ -641,13 +641,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1">
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1">
         <v>50</v>
@@ -656,10 +656,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1">
         <v>1.2</v>
@@ -670,13 +670,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1">
         <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
@@ -685,10 +685,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
